--- a/src/salary-data/2026.09/2026.09-喜多　弥史.xlsx
+++ b/src/salary-data/2026.09/2026.09-喜多　弥史.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>24:48</t>
+          <t>2:10</t>
         </is>
       </c>
       <c r="C5" s="16" t="n">
